--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.41620068469219</v>
+        <v>13.71763261126248</v>
       </c>
       <c r="D2" t="n">
-        <v>84.84269951763041</v>
+        <v>13.78693867161494</v>
       </c>
       <c r="E2" t="n">
-        <v>30.68366977072998</v>
+        <v>4.986096337743622</v>
       </c>
       <c r="F2" t="n">
-        <v>30.68523969987115</v>
+        <v>4.986351451229062</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04886114323222</v>
+        <v>3.745439935775236</v>
       </c>
       <c r="D3" t="n">
-        <v>23.47222011788811</v>
+        <v>3.814235769156819</v>
       </c>
       <c r="E3" t="n">
-        <v>30.68366977072998</v>
+        <v>4.986096337743622</v>
       </c>
       <c r="F3" t="n">
-        <v>30.68523969987115</v>
+        <v>4.986351451229062</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
